--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,25 +37,64 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>عصير تانج برتقال ظرف - 20 جم</t>
-  </si>
-  <si>
-    <t>كوكا كولا - 1.45 لتر</t>
-  </si>
-  <si>
-    <t>سبرايت - 1.45 لتر</t>
-  </si>
-  <si>
-    <t>كوكا كولا - 2.45 لتر</t>
-  </si>
-  <si>
-    <t>مسحوق غسيل فل ازرق يدوى - 9 كجم</t>
-  </si>
-  <si>
-    <t>مولتو ماجنم شوكولاتة بالبندق - 15 جنية</t>
-  </si>
-  <si>
-    <t>XXL مولتو شيكولاته بالبندق  - 10 جنية</t>
+    <t>جبنة دومتى فيتا بلس - 125 جم</t>
+  </si>
+  <si>
+    <t>مارى بسكويت- 15 جنية</t>
+  </si>
+  <si>
+    <t>بسكاتو بسكويت كريمة شيكولاتة- 60 جرام</t>
+  </si>
+  <si>
+    <t>دومتي عصير أناناس- 1 لتر</t>
+  </si>
+  <si>
+    <t>بسكويت بالزبدة 250جرام - 18 قطعه</t>
+  </si>
+  <si>
+    <t>بسكويت برتقال  250جرام - 18 قطعه</t>
+  </si>
+  <si>
+    <t>بسكويت جوزهند 250جرام - 18 قطعه</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس بالزيتون  - 250 مل</t>
+  </si>
+  <si>
+    <t>جبنة دومتي بلس بالزيتون - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة اسطنبولي بلس - 250 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة اسطنبولي بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فلمنك - 250 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فلمنك - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس بسطرمة - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس رومي - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس شيدر - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس لايت - 250 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس لايت - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنه دومتى جولد -- 250 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -416,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -444,138 +483,427 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>201</v>
+        <v>903</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>101.25</v>
+        <v>388</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>201</v>
+        <v>2989</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1012.5</v>
+        <v>504</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>1504</v>
+        <v>2989</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>2497</v>
+        <v>3024</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>191.25</v>
+        <v>333</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>2778</v>
+        <v>3024</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>222.5</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>2805</v>
+        <v>3863</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>162</v>
+        <v>289</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>5453</v>
+        <v>13853</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>289.75</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>11848</v>
+        <v>13853</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>197</v>
+        <v>528</v>
       </c>
       <c r="E9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>13854</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>528</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>13854</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>13855</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>13855</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>528</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19981</v>
+      </c>
+      <c r="B14" t="s">
         <v>14</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>451.5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19982</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>508.5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19983</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>451.5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>19984</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>508.5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>19985</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>451.5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>19986</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>508.5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19987</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>451.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>19989</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>451.5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>19991</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>451.5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>19993</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>451.5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>19996</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>508.5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>19997</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>451.5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>26103</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>647.5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,13 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>لبن بخيره - 500 مل</t>
+    <t>مرقة دجاج كنور فاين فودز شريط - 8 جم</t>
+  </si>
+  <si>
+    <t>جبنة رودس فيتا بيضاء - 250 جم</t>
+  </si>
+  <si>
+    <t>اوكسي يدوي 32 كيس - 50 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,19 +432,87 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>40.75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>159</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>366.75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>159</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>500</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D4">
+        <v>733.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>3477</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>566.75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21793</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>124</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مرقة دجاج كنور فاين فودز شريط - 8 جم</t>
-  </si>
-  <si>
-    <t>جبنة رودس فيتا بيضاء - 250 جم</t>
-  </si>
-  <si>
-    <t>اوكسي يدوي 32 كيس - 50 جم</t>
+    <t>حفاضات جود كير مقاس 5 - 40 حفاضة</t>
+  </si>
+  <si>
+    <t>مكرونة بساطة شعرية - 350 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,87 +429,53 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>159</v>
+        <v>2424</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>40.75</v>
+        <v>863.75</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>159</v>
+        <v>2424</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="D3">
-        <v>366.75</v>
+        <v>172.75</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>159</v>
+        <v>7704</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>733.5</v>
+        <v>171.75</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>3477</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>566.75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21793</v>
-      </c>
-      <c r="B6" t="s">
         <v>9</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>124</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,19 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>حفاضات جود كير مقاس 5 - 40 حفاضة</t>
-  </si>
-  <si>
-    <t>مكرونة بساطة شعرية - 350 جم</t>
+    <t>أولويز ماكسى  سميكة ناعمة بلمسة الألوڤيرا طويلة - 8 فوطة</t>
+  </si>
+  <si>
+    <t>فيبا سائل أطباق تفاح- 4 كجم</t>
+  </si>
+  <si>
+    <t>مناديل فاميليا جيب 2 طبقة - 10 منديل</t>
+  </si>
+  <si>
+    <t>سائل اطباق وفير بلس ليمون اصفر - 40 جم</t>
+  </si>
+  <si>
+    <t>اندومى سوبر مى خضار - 5 جنيه - 56 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,53 +438,104 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>2424</v>
+        <v>4372</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>863.75</v>
+        <v>27.25</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>2424</v>
+        <v>4372</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>172.75</v>
+        <v>436</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>7704</v>
+        <v>5517</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>171.75</v>
+        <v>360</v>
       </c>
       <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>11089</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>175.25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>11677</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>65</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>24257</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>209</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,19 +37,25 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>أولويز ماكسى  سميكة ناعمة بلمسة الألوڤيرا طويلة - 8 فوطة</t>
-  </si>
-  <si>
-    <t>فيبا سائل أطباق تفاح- 4 كجم</t>
-  </si>
-  <si>
-    <t>مناديل فاميليا جيب 2 طبقة - 10 منديل</t>
-  </si>
-  <si>
-    <t>سائل اطباق وفير بلس ليمون اصفر - 40 جم</t>
-  </si>
-  <si>
-    <t>اندومى سوبر مى خضار - 5 جنيه - 56 جم</t>
+    <t>ارز حبوبة رفيع - 1 كجم</t>
+  </si>
+  <si>
+    <t>لبن المراعى كامل دسم بلاستيك - 1 لتر</t>
+  </si>
+  <si>
+    <t>فانتا برتقال -- 1.45 لتر</t>
+  </si>
+  <si>
+    <t>صلصة هاينز - 360 جم</t>
+  </si>
+  <si>
+    <t>مسحوق غسيل فل ازرق يدوى - 2.5 كجم</t>
+  </si>
+  <si>
+    <t>صابون كامى رومانسية - 110 جم</t>
+  </si>
+  <si>
+    <t>بريكس مزيل بقع - 30 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -410,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -438,104 +444,138 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>4372</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>27.25</v>
+        <v>253</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>4372</v>
+        <v>990</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>436</v>
+        <v>558</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>5517</v>
+        <v>2774</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>360</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>11089</v>
+        <v>3478</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>175.25</v>
+        <v>382.5</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>11677</v>
+        <v>3934</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>65</v>
+        <v>51.25</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24257</v>
+        <v>8286</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>209</v>
+        <v>717</v>
       </c>
       <c r="E7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>8286</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>59.75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>12503</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>139</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,25 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>ارز حبوبة رفيع - 1 كجم</t>
-  </si>
-  <si>
-    <t>لبن المراعى كامل دسم بلاستيك - 1 لتر</t>
-  </si>
-  <si>
-    <t>فانتا برتقال -- 1.45 لتر</t>
-  </si>
-  <si>
-    <t>صلصة هاينز - 360 جم</t>
-  </si>
-  <si>
-    <t>مسحوق غسيل فل ازرق يدوى - 2.5 كجم</t>
-  </si>
-  <si>
-    <t>صابون كامى رومانسية - 110 جم</t>
-  </si>
-  <si>
-    <t>بريكس مزيل بقع - 30 جم</t>
+    <t>جبنة عبور لاند رومى - 250 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -416,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -444,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>3</v>
+        <v>5646</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -453,129 +435,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>253</v>
+        <v>525.5</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>990</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>558</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>2774</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>185</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>3478</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>382.5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>3934</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>51.25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>8286</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>717</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>8286</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>59.75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>12503</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>139</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,25 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>كوكا كولا جيب - 240 مل</t>
+    <t>بيبسى كانز جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>سردين دولفين بارد - 125 جم</t>
+  </si>
+  <si>
+    <t>سائل اطباق وفير بلس ليمون اخضر - 4 كجم</t>
+  </si>
+  <si>
+    <t>كل يوم عصير مانجو - 200 مل</t>
+  </si>
+  <si>
+    <t>ماكسى كانز برتقال اورجينال - 300 مل</t>
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -398,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +441,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>615</v>
+        <v>434</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,10 +450,129 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>305.5</v>
+        <v>303.5</v>
       </c>
       <c r="E2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>1409</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
+      </c>
+      <c r="C3">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>1350</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>1409</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>33.75</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>1409</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1687.5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>1409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>506.25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>1691</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>322</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>11838</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>113.5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23661</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>275.75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,25 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بيبسى كانز جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>سردين دولفين بارد - 125 جم</t>
-  </si>
-  <si>
-    <t>سائل اطباق وفير بلس ليمون اخضر - 4 كجم</t>
-  </si>
-  <si>
-    <t>كل يوم عصير مانجو - 200 مل</t>
-  </si>
-  <si>
-    <t>ماكسى كانز برتقال اورجينال - 300 مل</t>
+    <t>مسحوق باهي يدوي لافندر  - 60 جم</t>
   </si>
   <si>
     <t>YES</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -413,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -441,138 +426,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>434</v>
+        <v>24567</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>303.5</v>
+        <v>88.75</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>1409</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>16</v>
-      </c>
-      <c r="D3">
-        <v>1350</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>1409</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>11</v>
-      </c>
-      <c r="D4">
-        <v>33.75</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>1409</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1687.5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>1409</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>506.25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>1691</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>322</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>11838</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>113.5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23661</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>275.75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,52 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مسحوق باهي يدوي لافندر  - 60 جم</t>
+    <t>شويبس جولد خوخ - 950 مل</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>ديرى  مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا  - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا  - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 125 جرام</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,19 +471,325 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24567</v>
+        <v>8651</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>160</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21704</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>88.75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D3">
+        <v>693</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21704</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>19.25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21706</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>26.75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21706</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>963</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21712</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>13.5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21712</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>486</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21745</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>417.5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21752</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>474.25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21771</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>417.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21773</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>368.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21774</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>474.25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21777</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>368.5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21778</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>474.25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21779</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>417.5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>21781</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>283</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>21783</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>356.5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>21789</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>310</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>22126</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>368.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,52 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>شويبس جولد خوخ - 950 مل</t>
-  </si>
-  <si>
-    <t>باندا مثلثات - 8 قطعه</t>
-  </si>
-  <si>
-    <t>باندا جورمية مثلثات - 8 قطعه</t>
-  </si>
-  <si>
     <t>ديرى  مثلثات - 8 قطعه</t>
-  </si>
-  <si>
-    <t>جبنة باندا فيتا  - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا رومى - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا رومى - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا شيدر  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا شيدر - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا بسطرمة  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا بسطرمة - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا بسطرمة - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا  - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا فيتا 125 جرام</t>
   </si>
   <si>
     <t>YES</t>
@@ -443,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -471,325 +426,36 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>8651</v>
+        <v>21712</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>160</v>
+        <v>486</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21704</v>
+        <v>21712</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>13.5</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>693</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21704</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>19.25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21706</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>26.75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21706</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>963</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21712</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>13.5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21712</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>486</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21745</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>417.5</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21752</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>474.25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21771</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>417.5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21773</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>368.5</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21774</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>474.25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21777</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>368.5</v>
-      </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21778</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>474.25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21779</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>417.5</v>
-      </c>
-      <c r="E16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>21781</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <v>283</v>
-      </c>
-      <c r="E17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>21783</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>356.5</v>
-      </c>
-      <c r="E18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>21789</v>
-      </c>
-      <c r="B19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>310</v>
-      </c>
-      <c r="E19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>22126</v>
-      </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
-        <v>368.5</v>
-      </c>
-      <c r="E20" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,61 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>ديرى  مثلثات - 8 قطعه</t>
+    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 2.1 لتر</t>
+  </si>
+  <si>
+    <t>زيت هدية خليط- 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>زيت ريحانة دوار الشمس بيور - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس - 5 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1.8 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 2.4 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 2.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 700 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +480,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21712</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,27 +489,316 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>486</v>
+        <v>866</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21712</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>13.5</v>
+        <v>625</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>471</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>612.25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>479</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>878.75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>823</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>764.5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>1448</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>730.5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>1490</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>604</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>1492</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>860</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>2879</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>810</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>2935</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>892.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>6496</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>758</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>6497</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>855</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>7324</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>480.5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>9070</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>895</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>9358</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>554</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>11402</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>704</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>11962</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>681.75</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>11965</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>705.25</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>12924</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>600</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,61 +37,34 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال الممتاز خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت قلية خليط - 2.1 لتر</t>
-  </si>
-  <si>
-    <t>زيت هدية خليط- 1 لتر</t>
-  </si>
-  <si>
     <t>زيت حبوبة خليط - 900 مل</t>
   </si>
   <si>
-    <t>زيت ريحانة دوار الشمس بيور - 700 مل</t>
-  </si>
-  <si>
     <t>زيت حبوبة خليط - 700 مل</t>
   </si>
   <si>
-    <t>زيت حبوبة خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
-  </si>
-  <si>
     <t>سندة زيت خليط - 900 مل</t>
   </si>
   <si>
-    <t>سندة زيت خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس - 5 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 1.8 لتر</t>
-  </si>
-  <si>
     <t>زيت حبوبة خليط - 2.4 لتر</t>
   </si>
   <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال الممتاز خليط - 2.5 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 700 مل</t>
+    <t>دومتي جبنة فيتا بلس - 250 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس بالزيتون  - 250 مل</t>
+  </si>
+  <si>
+    <t>دومتي جبنة اسطنبولي بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فلمنك - 250 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس بسطرمة - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنه دومتى جولد -- 250 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -452,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -480,7 +453,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>9</v>
+        <v>823</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -489,15 +462,15 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>866</v>
+        <v>777</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>448</v>
+        <v>1490</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -506,15 +479,15 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>471</v>
+        <v>6496</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -523,15 +496,15 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>612.25</v>
+        <v>772</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>479</v>
+        <v>11402</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -540,265 +513,112 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>878.75</v>
+        <v>717</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>823</v>
+        <v>19980</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>764.5</v>
+        <v>519</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>1448</v>
+        <v>19982</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>730.5</v>
+        <v>519</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>1490</v>
+        <v>19985</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>604</v>
+        <v>460</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>1492</v>
+        <v>19986</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>860</v>
+        <v>519</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>2879</v>
+        <v>19989</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>810</v>
+        <v>460</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>2935</v>
+        <v>26103</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>892.5</v>
+        <v>654</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>6496</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>758</v>
-      </c>
-      <c r="E12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>6497</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>855</v>
-      </c>
-      <c r="E13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>7324</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>480.5</v>
-      </c>
-      <c r="E14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>9070</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>895</v>
-      </c>
-      <c r="E15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>9358</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>554</v>
-      </c>
-      <c r="E16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>11402</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>704</v>
-      </c>
-      <c r="E17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>11962</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>681.75</v>
-      </c>
-      <c r="E18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>11965</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>705.25</v>
-      </c>
-      <c r="E19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>12924</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>600</v>
-      </c>
-      <c r="E20" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1123.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,34 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت حبوبة خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 2.4 لتر</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس - 250 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بالزيتون  - 250 مل</t>
-  </si>
-  <si>
-    <t>دومتي جبنة اسطنبولي بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فلمنك - 250 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بسطرمة - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنه دومتى جولد -- 250 جم</t>
+    <t>دومتي عصير تفاح- 1 لتر</t>
+  </si>
+  <si>
+    <t>دومتي عصير أناناس- 1 لتر</t>
   </si>
   <si>
     <t>YES</t>
@@ -425,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -453,172 +429,36 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>823</v>
+        <v>3856</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>777</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>1490</v>
+        <v>3863</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>620</v>
+        <v>290</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>6496</v>
-      </c>
-      <c r="B4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>772</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>11402</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>717</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19980</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>519</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19982</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>519</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19985</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>460</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19986</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>519</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19989</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>460</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>26103</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>654</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
